--- a/firm3.xlsx
+++ b/firm3.xlsx
@@ -5509,7 +5509,11 @@
           <t>CONTINENTAL AG, SOUTH ACQUISITION CORP., CARLYLE CIM AGENT LLC Y EPD HOLDINGS INC.</t>
         </is>
       </c>
-      <c r="F135" s="2" t="n"/>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>[{"rol": null, "nombre": "V. CONCLUSIONES Número: IF-2017-26643403-APN-CNDC#MP"}, {"rol": null, "nombre": "VISTO FINANZAS PÚBLICAS"}, {"rol": null, "nombre": "COMPETENCIA, MINISTERIO DE PRODUCCIÓN"}, {"rol": null, "nombre": "AKTIENGESELLSCHAFT"}]</t>
+        </is>
+      </c>
       <c r="G135" s="3" t="n">
         <v>42041</v>
       </c>
@@ -8210,7 +8214,11 @@
           <t>WILLIS GROUP HOLDINGS PUBLIC LIMITED COMPANY Y TOWERS WATSON &amp; CO.</t>
         </is>
       </c>
-      <c r="F197" s="2" t="n"/>
+      <c r="F197" s="2" t="inlineStr">
+        <is>
+          <t>[{"rol": null, "nombre": "V. CONCLUSIONES Número: IF-2017-24560770-APN-CNDC#MP"}, {"rol": null, "nombre": "COMPETENCIA, MINISTERIO DE PRODUCCIÓN"}, {"rol": null, "nombre": "WATSON &amp; CO."}, {"rol": null, "nombre": "Que, TOWERS WATSON &amp; CO."}, {"rol": null, "nombre": "Que, TOWERS WATSON PLC., POR CIENTO (50,1 %) CUARENTA Y NUEVE COMA NUEVE POR CIENTO (49,9 %)"}, {"rol": null, "nombre": "DOSCIENTOS MILLONES ($ 200.000.000)"}, {"rol": null, "nombre": "TOWERS WATSON &amp; CO."}]</t>
+        </is>
+      </c>
       <c r="G197" s="3" t="n">
         <v>42380</v>
       </c>
@@ -15967,7 +15975,11 @@
           <t>MINERA TRITON ARGENTINA S.A. Y PATAGONIA GOLD S.A.</t>
         </is>
       </c>
-      <c r="F369" s="2" t="n"/>
+      <c r="F369" s="2" t="inlineStr">
+        <is>
+          <t>[{"rol": null, "nombre": "Número: IF-2017-18041377-APN-CNDC#MP"}, {"rol": null, "nombre": "COMPETENCIA, MINISTERIO DE PRODUCCIÓN"}, {"rol": null, "nombre": "Que MINERA TRITON ARGENTINA S.A."}, {"rol": null, "nombre": "Que COSE, PATAGONIA GOLD S.A."}, {"rol": null, "nombre": "DOSCIENTOS MILLONES ($ 200.000.000), Que"}, {"rol": null, "nombre": "SIETE (7)"}]</t>
+        </is>
+      </c>
       <c r="H369" s="3" t="n">
         <v>42971</v>
       </c>
@@ -16374,7 +16386,11 @@
           <t>F.H.B. INVERSORA S.A., MOÑO AZUL SOCIEDAD ANONIMA, COMERCIAL, INDUSTRIAL Y AGROPECUARIA Y EXPOFRUT ARGENTINA S.A.</t>
         </is>
       </c>
-      <c r="F377" s="2" t="n"/>
+      <c r="F377" s="2" t="inlineStr">
+        <is>
+          <t>[{"rol": null, "nombre": "BRENT S.A."}, {"rol": null, "nombre": "MURCHINSON DEPOSITO FISCAL BUENOS AIRES (UTE) (comprador)"}, {"rol": null, "nombre": "DEPOSITO FISCAL BS. AS. – MURCHINSON (UTE) (comprador)"}, {"rol": null, "nombre": "PATAGONIA NORTE (target)"}]</t>
+        </is>
+      </c>
       <c r="H377" s="3" t="n">
         <v>43034</v>
       </c>
@@ -16806,7 +16822,11 @@
           <t>GRI RENEWABLE INDUSTRIES, S.L., METALÚRGICA CALVIÑO S.A, GASTÓN MAXIMILIANO GUARINO Y MAURO EMANUEL GUARINO</t>
         </is>
       </c>
-      <c r="F385" s="2" t="n"/>
+      <c r="F385" s="2" t="inlineStr">
+        <is>
+          <t>[{"rol": null, "nombre": "GESTAMP BAIRES S.A."}, {"rol": null, "nombre": "GESTAMP CORDOBA S.A."}, {"rol": null, "nombre": "GONVARRI ARGENTINA S.A."}]</t>
+        </is>
+      </c>
       <c r="H385" s="3" t="n">
         <v>43020</v>
       </c>
@@ -19335,7 +19355,11 @@
           <t>DAMIÁN BURGIO, IGNACIO JORGE ROSNER Y GRUPO INDALO</t>
         </is>
       </c>
-      <c r="F430" s="2" t="n"/>
+      <c r="F430" s="2" t="inlineStr">
+        <is>
+          <t>[{"rol": null, "nombre": "FDS, CML"}, {"rol": null, "nombre": "INVERSIONES S.A., GLOBAL INVESTMENT S.A."}, {"rol": null, "nombre": "Rivadavia. SMI EDITORIAL AMFIN S.A."}, {"rol": null, "nombre": "IBEROAMERICANA DE COMUNICACIONES S.A."}, {"rol": null, "nombre": "IBEROAMERICANA DE MEDIOS S.A., A S.A."}, {"rol": null, "nombre": "MINUTO 1”. Los"}, {"rol": null, "nombre": "CORP S.A."}, {"rol": null, "nombre": "CARRANZA S.A. HIDROCUYO SA."}, {"rol": null, "nombre": "III.1. El"}, {"rol": null, "nombre": "EX-2017-27178347—APN-DDYME#MP"}, {"rol": null, "nombre": "COMPETENCIA"}]</t>
+        </is>
+      </c>
       <c r="H430" s="3" t="n">
         <v>43735</v>
       </c>
@@ -27491,7 +27515,11 @@
           <t>SIKA AG Y FINANCIÈRE SANTEC S.A.</t>
         </is>
       </c>
-      <c r="F578" s="2" t="n"/>
+      <c r="F578" s="2" t="inlineStr">
+        <is>
+          <t>[{"rol": null, "nombre": "SIKA S.A.I.C."}, {"rol": null, "nombre": "VDP LOGÍSTICA S.A."}]</t>
+        </is>
+      </c>
       <c r="G578" s="3" t="n">
         <v>43550</v>
       </c>
@@ -29195,7 +29223,11 @@
           <t>CONC. 1726 GARRUCHOS S.A. Y GRUPO BENICIO S.A.</t>
         </is>
       </c>
-      <c r="F609" s="2" t="n"/>
+      <c r="F609" s="2" t="inlineStr">
+        <is>
+          <t>[{"rol": null, "nombre": "PRODUCTORA DEL NOROESTE S.A."}, {"rol": null, "nombre": "NORTE S.A."}]</t>
+        </is>
+      </c>
       <c r="H609" s="3" t="n">
         <v>46045</v>
       </c>
@@ -37528,7 +37560,11 @@
           <t>LOS LAPACHOS S.A.</t>
         </is>
       </c>
-      <c r="F757" s="2" t="n"/>
+      <c r="F757" s="2" t="inlineStr">
+        <is>
+          <t>[{"rol": null, "nombre": "BIZLAND"}, {"rol": null, "nombre": "SUPERCABLECANAL S.A."}, {"rol": null, "nombre": "CABLECORP S.A., SAN LUIS CABLE S.A., BTC S.A., TELE IMAGEN CODIFICADA S.A., SURCOR TV S.A., RTC S.A., TAJAMAR SISTEMAS ELECTRÓNICOS S.A., ARLINK S.A."}, {"rol": null, "nombre": "SUPERFONE S.A., T.V. CA S.A., FIBRA IMAGEN RIO CUARTO S.A., VICUÑA TV S.A., TRASLASIERRA CABLE COLOR S.A., RED HORSE S.A."}, {"rol": null, "nombre": "CENTRO CARD"}, {"rol": null, "nombre": "TALKING AMERICAN"}, {"rol": null, "nombre": "IDEAS PARA COMUNICAR"}, {"rol": null, "nombre": "LOS CARDOS"}]</t>
+        </is>
+      </c>
       <c r="G757" s="3" t="n">
         <v>44907</v>
       </c>
@@ -38743,7 +38779,11 @@
           <t>SAVENCIA FROMAGE &amp; DAIRY INTERNATIONAL S.A.S.</t>
         </is>
       </c>
-      <c r="F779" s="2" t="n"/>
+      <c r="F779" s="2" t="inlineStr">
+        <is>
+          <t>[{"rol": null, "nombre": "MILKAUT S.A."}, {"rol": null, "nombre": "PETRA S.A."}, {"rol": null, "nombre": "ARMOR PROTEINES S.A.S. Venta POLENGHI INDUSTRIAS ALIMENTICIAS Ltda."}, {"rol": null, "nombre": "REPUBLICA DEL CACAO CACAOREPUBLIC Cía. Ltda."}, {"rol": null, "nombre": "SAVENCIA PRODUITS LAITIERS INTERNATIONAL S.A.S."}, {"rol": null, "nombre": "VALRHONA S.A.S."}]</t>
+        </is>
+      </c>
       <c r="H779" s="3" t="n">
         <v>45530</v>
       </c>
@@ -39364,7 +39404,11 @@
           <t>CAPEX S.A. Y TRAFIGURA ARGENTINA S.A</t>
         </is>
       </c>
-      <c r="F790" s="2" t="n"/>
+      <c r="F790" s="2" t="inlineStr">
+        <is>
+          <t>[{"rol": null, "nombre": "TRAFIGURA ARGENTINA S.A."}, {"rol": null, "nombre": "LUBRICANTES AVELLANEDA S.A.U."}, {"rol": null, "nombre": "REFINERÍA BAHÍA BLANCA S.A.U."}, {"rol": null, "nombre": "PETROMINING S.A."}, {"rol": null, "nombre": "TRAFIGURA S.A."}, {"rol": null, "nombre": "PUERTO CAMPANA S.A.)"}, {"rol": null, "nombre": "IMPALA TERMINALS ARGENTINA S.A."}]</t>
+        </is>
+      </c>
       <c r="G790" s="3" t="n">
         <v>45112</v>
       </c>
@@ -40932,7 +40976,11 @@
         </is>
       </c>
       <c r="E819" s="2" t="n"/>
-      <c r="F819" s="2" t="n"/>
+      <c r="F819" s="2" t="inlineStr">
+        <is>
+          <t>[{"rol": null, "nombre": "Número: IF-2024-32144017-APN-DNCE#CNDC"}, {"rol": null, "nombre": "Que (PROSUM)"}, {"rol": null, "nombre": "Que MINISTERIO DE ECONOMÍA, COMPETENCIA"}, {"rol": null, "nombre": "COMISIÓN NACIONAL DE DEFENSA DE LA COMPETENCIA"}, {"rol": null, "nombre": "CNDC#MEC"}, {"rol": null, "nombre": "COMPETENCIA Ley 27.442."}, {"rol": null, "nombre": "INVERSIONES Y REPRESENTACIONES S.A."}]</t>
+        </is>
+      </c>
       <c r="G819" s="3" t="n">
         <v>45261</v>
       </c>
@@ -42554,7 +42602,11 @@
           <t>FIDEICOMISO FARMAPLUS I Y FIDEICOMISO MANU SEGURA</t>
         </is>
       </c>
-      <c r="F850" s="2" t="n"/>
+      <c r="F850" s="2" t="inlineStr">
+        <is>
+          <t>[{"rol": null, "nombre": "SUPERFARMA S.A."}, {"rol": null, "nombre": "VILLACH S.R.L."}, {"rol": null, "nombre": "FARMACIA DANESA S.R.L."}, {"rol": null, "nombre": "PEDIDOS FARMA S.A."}, {"rol": null, "nombre": "SUPERBUT S.A."}, {"rol": null, "nombre": "MACUSEG S.A."}, {"rol": null, "nombre": "EMPRENDIMIENTOS CARMAN S.A."}, {"rol": null, "nombre": "AZUL ACE"}, {"rol": null, "nombre": "LOWSEDO S.R.L."}, {"rol": null, "nombre": "L´OCCITANIA S.R.L."}, {"rol": null, "nombre": "MARAGUNIC S.R.L."}, {"rol": null, "nombre": "AGUNICMAR S.R.L."}, {"rol": null, "nombre": "CLADIL S.R.L."}, {"rol": null, "nombre": "FARMACIA AVENIDA ENTRE RÍOS 299 S.C.S."}, {"rol": null, "nombre": "FARMACIAS LIDER"}]</t>
+        </is>
+      </c>
       <c r="H850" s="3" t="n">
         <v>46008</v>
       </c>
@@ -44507,7 +44559,11 @@
           <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
-      <c r="F886" s="2" t="n"/>
+      <c r="F886" s="2" t="inlineStr">
+        <is>
+          <t>[{"rol": null, "nombre": "DELTA AIR LINES, INC."}, {"rol": null, "nombre": "LATAM AIRLINES GROUP S.A.3 (CHILE/ARGENTINA)"}, {"rol": null, "nombre": "TAM LINHAS AÉREAS S.A. (BRASIL)"}, {"rol": null, "nombre": "LATAM AIRLINES PERÚ S.A. (PERÚ)"}, {"rol": null, "nombre": "LATAM- AIRLINES ECUADOR S.A. D/B/A LATAM AIRLINES ECUADOR (ECUADOR)"}, {"rol": null, "nombre": "ABSA AEROLINHAS BRASILEIRAS S.A."}, {"rol": null, "nombre": "BRASIL)"}, {"rol": null, "nombre": "LAN CARGO S.A. (CHILE)"}, {"rol": null, "nombre": "LATAM TRAVEL S.A."}]</t>
+        </is>
+      </c>
       <c r="H886" s="3" t="n">
         <v>46107</v>
       </c>
@@ -45157,7 +45213,11 @@
           <t>BUENOS AIRES SERVICIOS DE SALUD (BASA) S.A. UTE</t>
         </is>
       </c>
-      <c r="F899" s="2" t="n"/>
+      <c r="F899" s="2" t="inlineStr">
+        <is>
+          <t>[{"rol": null, "nombre": "POLICLINICO REGIONAL AVELLANEDA S.A."}, {"rol": null, "nombre": "LOGIMED S.A."}, {"rol": null, "nombre": "ANIVA S.A."}, {"rol": null, "nombre": "WELL BEING S.A."}, {"rol": null, "nombre": "BUENOS AIRES SERVICIOS DE SALUD BASA S.A."}, {"rol": null, "nombre": "ADMINISTRACION SALUD S.A."}, {"rol": null, "nombre": "BASA SAN JUAN S.A."}, {"rol": null, "nombre": "REDEXIR S.A."}, {"rol": null, "nombre": "ZONA OESTE SALUD S.A."}, {"rol": null, "nombre": "HOGAR SALUD S.A."}, {"rol": null, "nombre": "DACARI SALUD S.A."}, {"rol": null, "nombre": "PRAXISMED S.R.L."}, {"rol": null, "nombre": "FUNDACION FRAY LUIS BELTRAN"}, {"rol": null, "nombre": "C.E.T.E.T. S.R.L."}, {"rol": null, "nombre": "KILAB S.R.L."}, {"rol": null, "nombre": "BIOSALUD S.R.L."}, {"rol": null, "nombre": "HITRA S.A."}, {"rol": null, "nombre": "REVERSA S.A."}, {"rol": null, "nombre": "SANIRAP S.A."}, {"rol": null, "nombre": "RED DIALMED S.A."}, {"rol": null, "nombre": "INSTITUTO PRIVADO DE NEFROLOGIA S.A."}, {"rol": null, "nombre": "CETER S.A."}, {"rol": null, "nombre": "SANATORIO GENERAL SARMIENTO CLINICA PRIVADA S.R.L."}, {"rol": null, "nombre": "GLOBAL MED S.A."}, {"rol": null, "nombre": "KLP CORP S.A."}, {"rol": null, "nombre": "KCBD CORP S.A."}, {"rol": null, "nombre": "INCON S.R.L."}, {"rol": null, "nombre": "BROWN S.R.L."}, {"rol": null, "nombre": "RASON PROPIEDADES S.A."}, {"rol": null, "nombre": "MEDICAMENTUM S.A."}, {"rol": null, "nombre": "CENTROMET S.A."}, {"rol": null, "nombre": "FARMACIA EL POLICLINICO S.R.L."}, {"rol": null, "nombre": "EVOLUCION SEGUROS S.A."}, {"rol": null, "nombre": "NALU EXCLUSIVO PRODUCTORES ASC. DE SEGUROS S.A."}, {"rol": null, "nombre": "SOFRE DIGITAL S.A."}, {"rol": null, "nombre": "SOFRE NETWORK S.A."}, {"rol": null, "nombre": "ALTA DENSIDAD S.A."}, {"rol": null, "nombre": "BAE NEGOCIOS S.A."}, {"rol": null, "nombre": "ESTRELLAS SATELITAL S.A."}, {"rol": null, "nombre": "EDITORIAL ACONCAGUA S.A."}, {"rol": null, "nombre": "EDITORIAL SARMIENTO S.A."}, {"rol": null, "nombre": "NEXTV S.A."}, {"rol": null, "nombre": "CM TV &amp; PUBLICIDAD S.A."}, {"rol": null, "nombre": "MARKETING &amp; PUBLICIDAD S.R.L."}, {"rol": null, "nombre": "EDITORIAL MANUEL BELGRANO S.A."}, {"rol": null, "nombre": "SEND TV S.A."}, {"rol": null, "nombre": "INSTITUTO SUPERIOR CRONICA"}, {"rol": null, "nombre": "LA OPINIÓN AUSTRAL S.A.S."}, {"rol": null, "nombre": "LA OPINION AUSTRAL S.A."}, {"rol": null, "nombre": "EDITORIAL SAN MARTIN S.A."}, {"rol": null, "nombre": "HOSPITAL UNIVERSITARIO DE LA FUNDACIÓN FAVALORO PARA LA DOCENCIA Y LA INVESTIGACIÓN MÉDICA"}, {"rol": null, "nombre": "FUNDACIÓN FAVALORO"}, {"rol": null, "nombre": "RED BASA"}]</t>
+        </is>
+      </c>
       <c r="G899" s="3" t="n">
         <v>45849</v>
       </c>
@@ -47030,7 +47090,11 @@
           <t>AKZO NOBEL N.V. Y DE AXALTA COATING SYSTEMS LTD.</t>
         </is>
       </c>
-      <c r="F933" s="2" t="n"/>
+      <c r="F933" s="2" t="inlineStr">
+        <is>
+          <t>[{"rol": null, "nombre": "AKZO NOBEL ARGENTINA S.A."}, {"rol": null, "nombre": "AKZO NOBEL COATINGS INC."}, {"rol": null, "nombre": "INTERNATIONAL PAINT LLC"}, {"rol": null, "nombre": "PINTURAS INCA S.A."}, {"rol": null, "nombre": "INTERQUIM S.A.S."}, {"rol": null, "nombre": "AXALTA COATING SYSTEMS ARGENTINA S.R.L."}, {"rol": null, "nombre": "AXALTA COATINGS SYSTEMS BRAZIL LTDA."}, {"rol": null, "nombre": "AXALTA COATING SYSTEMS MÉXICO S. DE R.L. DE C.V."}, {"rol": null, "nombre": "AXALTA COATING SYSTEMS GERMANY GMBH &amp; CO. KG"}, {"rol": null, "nombre": "AXALTA POWDER COATING SYSTEMS ANDINA S.A."}, {"rol": null, "nombre": "AXALTA POWDER COATING SYSTEMS COLOMBIA S.A.S."}]</t>
+        </is>
+      </c>
       <c r="H933" s="3" t="n">
         <v>46203</v>
       </c>
